--- a/data.xlsx
+++ b/data.xlsx
@@ -1,71 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="default_reader" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_key" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preserve_types" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>*** Tasks ***</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Row 1</t>
-  </si>
-  <si>
-    <t>Row 2</t>
-  </si>
-  <si>
-    <t>Row 3</t>
-  </si>
-  <si>
-    <t>Row 4</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="9"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4D7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,50 +125,172 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B8C8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B8C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B8C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B8C8"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -126,10 +299,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -167,71 +340,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -259,7 +432,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -282,11 +455,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -295,13 +468,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -311,7 +484,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -320,7 +493,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -329,7 +502,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -337,10 +510,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -405,70 +578,608 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="19.433571428571426" customWidth="1" bestFit="1"/>
+    <col width="17" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
+    <col width="6" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="23" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="38" customWidth="1" style="9" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="28" customHeight="1" s="9">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>*** Tasks ***</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1" s="9">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Value: int(A) + int(B)
+Expected: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="9">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Value: int(A) + int(B)
+Expected: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="9">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Value: int(A) + int(B)
+Expected: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="9">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>2001-05-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Value: int(A) + datetime(B)
+Expected: FAIL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="22" customWidth="1" style="9" min="1" max="2"/>
+    <col width="14" customWidth="1" style="9" min="2" max="2"/>
+    <col width="15" customWidth="1" style="9" min="3" max="3"/>
+    <col width="36" customWidth="1" style="9" min="4" max="4"/>
+    <col width="12" customWidth="1" style="9" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="9">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="9">
+      <c r="A2" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Gus</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Jencey</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>gjencey0@irs.gov</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="9">
+      <c r="A3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Muffin</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Di Angelo</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>mdiangelo1@ibm.com</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="9">
+      <c r="A4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Tally</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Klesel</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>tklesel2@hud.gov</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="9">
+      <c r="A5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Juliet</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Schuster</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>jschuster3@google.cn</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="9">
+      <c r="A6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Griz</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>MacNeilly</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>gmacneilly4@odnoklassniki.ru</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="9">
+      <c r="A7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Rosalie</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Rosell</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>rrosell5@examiner.com</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="9">
+      <c r="A8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Yanaton</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Greenrde</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>ygreenrde6@phoca.cz</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="9">
+      <c r="A9" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Karlen</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Dripps</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>kdripps7@surveymonkey.com</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Bigender</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="9">
+      <c r="A10" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Syman</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Nisuis</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>snisuis8@topsy.com</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="9">
+      <c r="A11" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Katy</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Edmondson</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>kedmondson9@mapquest.com</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="9">
+      <c r="A12" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Daria</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Fitzmaurice</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>dfitzmauricea@fema.gov</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Agender</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="9">
+      <c r="A13" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Ardyce</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Abram</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>aabramb@cnn.com</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="9">
+      <c r="A14" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Abrahan</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Redmore</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>aredmorec@businessweek.com</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="22" customWidth="1" style="9" min="1" max="1"/>
+    <col width="23" customWidth="1" style="9" min="2" max="2"/>
+    <col width="19" customWidth="1" style="9" min="3" max="3"/>
+    <col width="13.33203125" customWidth="1" style="9" min="4" max="4"/>
+    <col width="11.44140625" customWidth="1" style="9" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="9">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="9">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Data Type String</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Ant</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="9">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Data Type int</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="9">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Data Type float</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="9">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Data Type Data</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>37031</v>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="9">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Data Type Bool</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
